--- a/output/full_scan/batch_seq6_2026-08-10.xlsx
+++ b/output/full_scan/batch_seq6_2026-08-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6206</v>
+        <v>6183</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>781.4295398605429</v>
+        <v>759.0715295797295</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>158</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>69.8519648258317</v>
+        <v>57.72972358501564</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>22.36509063639624</v>
+        <v>24.80649994338685</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.2429539860543</v>
+        <v>0.8393055552133863</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>3.356136910500504</v>
+        <v>0.0516142484460759</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6183</v>
+        <v>6206</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>779.0715295797295</v>
+        <v>741.4295398605429</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>158</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>57.72972358501564</v>
+        <v>69.8519648258317</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>24.80649994338685</v>
+        <v>22.36509063639624</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.8393055552133863</v>
+        <v>2.2429539860543</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -623,11 +623,11 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.0516142484460759</v>
+        <v>3.356136910500504</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>739.9007446685157</v>
+        <v>699.9007446685157</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>80</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>694.298599291236</v>
+        <v>674.298599291236</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1040</v>
@@ -739,21 +739,21 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6426</v>
+        <v>6423</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>667.2407417551258</v>
+        <v>646.479123855205</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>217.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.00891190168468</v>
+        <v>62.04457810321975</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>23.59125144904065</v>
+        <v>24.75648321415393</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.528340892861066</v>
+        <v>2.364080393908019</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>8.13280202667679</v>
+        <v>1.871420111893109</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6423</v>
+        <v>6426</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>646.479123855205</v>
+        <v>627.2407417551258</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>217.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>62.04457810321975</v>
+        <v>65.00891190168468</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>24.75648321415393</v>
+        <v>23.59125144904065</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.364080393908019</v>
+        <v>3.528340892861066</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.871420111893109</v>
+        <v>8.13280202667679</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6213</v>
+        <v>6174</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>607.5732718092964</v>
+        <v>588.7947111834289</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>427.5</v>
+        <v>42.1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>68.17267535409505</v>
+        <v>42.64256723209201</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>21.01192449358658</v>
+        <v>27.08809261864932</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.939831190477381</v>
+        <v>0.6669427503235502</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>12.04988962019979</v>
+        <v>-0.2637432742458458</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6416</v>
+        <v>6213</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>599.7392298105297</v>
+        <v>567.5732718092964</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>103.5</v>
+        <v>427.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>61.07306364228874</v>
+        <v>68.17267535409505</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>22.36052036738694</v>
+        <v>21.01192449358658</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.8541636234026162</v>
+        <v>0.939831190477381</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4293684829413609</v>
+        <v>12.04988962019979</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6225</v>
+        <v>6416</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>597.5305158178907</v>
+        <v>559.7392298105297</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>27.7</v>
+        <v>103.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.86523044436224</v>
+        <v>61.07306364228874</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>14.97469433694032</v>
+        <v>22.36052036738694</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.371576731818218</v>
+        <v>0.8541636234026162</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2549384159791399</v>
+        <v>0.4293684829413609</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6174</v>
+        <v>6225</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>588.7947111834289</v>
+        <v>557.5305158178907</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>42.1</v>
+        <v>27.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>42.64256723209201</v>
+        <v>63.86523044436224</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>27.08809261864932</v>
+        <v>14.97469433694032</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.6669427503235502</v>
+        <v>1.371576731818218</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.2637432742458458</v>
+        <v>0.2549384159791399</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6165</v>
+        <v>6243</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>586.0837748536428</v>
+        <v>546.8279966440317</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>50.9</v>
+        <v>45.7</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>57.42647306499502</v>
+        <v>49.73499215487036</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15.63548067020227</v>
+        <v>24.50252557516282</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4083774853642788</v>
+        <v>0.4275410613229602</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.1674920369763979</v>
+        <v>-0.775992343674111</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6414</v>
+        <v>6165</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>578.6962739065256</v>
+        <v>546.0837748536428</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>482</v>
+        <v>50.9</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.98893928656253</v>
+        <v>57.42647306499502</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>22.63266797071104</v>
+        <v>15.63548067020227</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.5780998580566509</v>
+        <v>0.4083774853642788</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.853520720826112</v>
+        <v>0.1674920369763979</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6257</v>
+        <v>6173</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>574.4171668524763</v>
+        <v>541.4106605656436</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>207.5</v>
+        <v>168.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>48.23670684236492</v>
+        <v>42.68472073119765</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>20.23025813225657</v>
+        <v>34.40595260796817</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.105316696941825</v>
+        <v>1.192593663939603</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.5372968428071516</v>
+        <v>2.050485919277733</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6196</v>
+        <v>6414</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>550.7388291927062</v>
+        <v>538.6962739065256</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>507</v>
+        <v>482</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>48.94670338794104</v>
+        <v>63.98893928656253</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>18.17108286298426</v>
+        <v>22.63266797071104</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5649022304227247</v>
+        <v>0.5780998580566509</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.09659835150966239</v>
+        <v>1.853520720826112</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6173</v>
+        <v>6257</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>541.4106605656436</v>
+        <v>534.4171668524763</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>168.5</v>
+        <v>207.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>42.68472073119765</v>
+        <v>48.23670684236492</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>34.40595260796817</v>
+        <v>20.23025813225657</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.192593663939603</v>
+        <v>1.105316696941825</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>2.050485919277733</v>
+        <v>0.5372968428071516</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6191</v>
+        <v>6196</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>526.5213487682032</v>
+        <v>510.7388291927062</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>87.2</v>
+        <v>507</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>46.10082338888115</v>
+        <v>48.94670338794104</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>32.47729147557256</v>
+        <v>18.17108286298426</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.9069630681754032</v>
+        <v>0.5649022304227247</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.3827828243389604</v>
+        <v>0.09659835150966239</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6243</v>
+        <v>6207</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>516.8279966440317</v>
+        <v>493.1233910795527</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>45.7</v>
+        <v>107</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>49.73499215487036</v>
+        <v>45.35352010472476</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>24.50252557516282</v>
+        <v>24.01990798366345</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.4275410613229602</v>
+        <v>0.8414466540819895</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.775992343674111</v>
+        <v>0.0129623380944003</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6192</v>
+        <v>6191</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>512.8844005003289</v>
+        <v>486.5213487682032</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>116</v>
+        <v>87.2</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>50.71970970820144</v>
+        <v>46.10082338888115</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>27.63184573698078</v>
+        <v>32.47729147557256</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.803305208082017</v>
+        <v>0.9069630681754032</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.6284810867254307</v>
+        <v>0.3827828243389604</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6226</v>
+        <v>6188</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>511.1181302095761</v>
+        <v>474.8406128108113</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>21.4</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>51.85707165608408</v>
+        <v>49.80207136706857</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>21.64916109257221</v>
+        <v>25.52727840673741</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.7261193329042747</v>
+        <v>0.5760718298255886</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.0858684090367485</v>
+        <v>0.7769172661227373</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6202</v>
+        <v>6192</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>508.6656967592002</v>
+        <v>472.8844005003289</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>63.8</v>
+        <v>116</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>56.74697808965778</v>
+        <v>50.71970970820144</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>20.446544188162</v>
+        <v>27.63184573698078</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7603994648675344</v>
+        <v>1.803305208082017</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>1.117314594431419</v>
+        <v>0.6284810867254307</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6214</v>
+        <v>6226</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>505.1093242918259</v>
+        <v>471.1181302095761</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>144.5</v>
+        <v>21.4</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>51.90361828462773</v>
+        <v>51.85707165608408</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>13.55674118232764</v>
+        <v>21.64916109257221</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.7395676640936464</v>
+        <v>0.7261193329042747</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.0686585128964987</v>
+        <v>-0.0858684090367485</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6207</v>
+        <v>6202</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>493.1233910795527</v>
+        <v>468.6656967592002</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>107</v>
+        <v>63.8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45.35352010472476</v>
+        <v>56.74697808965778</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>24.01990798366345</v>
+        <v>20.446544188162</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.8414466540819895</v>
+        <v>0.7603994648675344</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0129623380944003</v>
+        <v>1.117314594431419</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6188</v>
+        <v>6269</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>474.8406128108113</v>
+        <v>467.3790662214192</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>49.80207136706857</v>
+        <v>59.06299385342777</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>25.52727840673741</v>
+        <v>23.02567040809344</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5760718298255886</v>
+        <v>1.755810145246609</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.7769172661227373</v>
+        <v>2.098634061476899</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6269</v>
+        <v>6214</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>467.3790662214192</v>
+        <v>465.1093242918259</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>144.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>59.06299385342777</v>
+        <v>51.90361828462773</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>23.02567040809344</v>
+        <v>13.55674118232764</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.755810145246609</v>
+        <v>0.7395676640936464</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>2.098634061476899</v>
+        <v>-0.0686585128964987</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6215</v>
+        <v>6204</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>444.0955443326735</v>
+        <v>434.4520395977325</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>102.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>54.4831845416134</v>
+        <v>49.38479745912756</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20.62292992617979</v>
+        <v>32.70946694624664</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.618470111238015</v>
+        <v>2.159783213308927</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.603861921628523</v>
+        <v>2.195641091635059</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6204</v>
+        <v>6456</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>434.4520395977325</v>
+        <v>429.5605218768488</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>49.38479745912756</v>
+        <v>55.7413526864353</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>32.70946694624664</v>
+        <v>19.71368861988782</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2.159783213308927</v>
+        <v>1.826702105975958</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>2.195641091635059</v>
+        <v>0.9622575759652472</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6451</v>
+        <v>6412</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>432.1336928623746</v>
+        <v>426.4269401657284</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>456</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>51.91723260762927</v>
+        <v>43.0442641973437</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>20.75121944207835</v>
+        <v>32.45947676384331</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.17541246209539</v>
+        <v>0.6196459418887108</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>11.18580724096196</v>
+        <v>0.3570158784420925</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6282</v>
+        <v>6215</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>430.5686398964842</v>
+        <v>404.0955443326735</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>50</v>
+        <v>102.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.06184388891582</v>
+        <v>54.4831845416134</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>22.93307245830036</v>
+        <v>20.62292992617979</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.04928995115029</v>
+        <v>1.618470111238015</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.7979662344550689</v>
+        <v>1.603861921628523</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6164</v>
+        <v>6227</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>429.9545860402761</v>
+        <v>400.5733654378773</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>11.8</v>
+        <v>125</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>42.92545485830978</v>
+        <v>59.6060879416657</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>28.85861796316664</v>
+        <v>14.62738190139732</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.2785208213487328</v>
+        <v>0.7786837377881891</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0073923597656112</v>
+        <v>1.726766377538268</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6412</v>
+        <v>6451</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>426.4269401657284</v>
+        <v>392.1336928623746</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>79.40000000000001</v>
+        <v>456</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>43.0442641973437</v>
+        <v>51.91723260762927</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>32.45947676384331</v>
+        <v>20.75121944207835</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6196459418887108</v>
+        <v>1.17541246209539</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.3570158784420925</v>
+        <v>11.18580724096196</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6271</v>
+        <v>6229</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>425.8236690474123</v>
+        <v>390.7053521503887</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>197</v>
+        <v>23.55</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>48.91352016282462</v>
+        <v>44.50445772105656</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23.13023124621723</v>
+        <v>23.71939551545771</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.9825193022842416</v>
+        <v>0.2669724967060971</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>3.554357245802505</v>
+        <v>0.1581766699771224</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6168</v>
+        <v>6282</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>405.5998715595856</v>
+        <v>390.5686398964842</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>25.05</v>
+        <v>50</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>50.14145864011715</v>
+        <v>51.06184388891582</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>21.92519634713251</v>
+        <v>22.93307245830036</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.920718696931504</v>
+        <v>1.04928995115029</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.3851070248310393</v>
+        <v>0.7979662344550689</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2223,21 +2223,21 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6456</v>
+        <v>6164</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>399.5605218768488</v>
+        <v>389.9545860402761</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>55.7413526864353</v>
+        <v>42.92545485830978</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>19.71368861988782</v>
+        <v>28.85861796316664</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.826702105975958</v>
+        <v>0.2785208213487328</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.9622575759652472</v>
+        <v>0.0073923597656112</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6190</v>
+        <v>6271</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>371.4921416834692</v>
+        <v>385.8236690474123</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>68.8</v>
+        <v>197</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>47.05627038961318</v>
+        <v>48.91352016282462</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>32.08947107167344</v>
+        <v>23.13023124621723</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.8270287635314424</v>
+        <v>0.9825193022842416</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.5251318219281336</v>
+        <v>3.554357245802505</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6449</v>
+        <v>6168</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>367.6955893517073</v>
+        <v>385.5998715595856</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>240.5</v>
+        <v>25.05</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>44.6919693221508</v>
+        <v>50.14145864011715</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>31.57261110678408</v>
+        <v>21.92519634713251</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7398891102966632</v>
+        <v>0.920718696931504</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>4.239608341688111</v>
+        <v>0.3851070248310393</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6224</v>
+        <v>6190</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>364.8592085479777</v>
+        <v>371.4921416834692</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>56</v>
+        <v>68.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>42.21910147936961</v>
+        <v>47.05627038961318</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>32.83834489354695</v>
+        <v>32.08947107167344</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4784450780377132</v>
+        <v>0.8270287635314424</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.8945242461589924</v>
+        <v>0.5251318219281336</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6166</v>
+        <v>6281</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>363.2439352713656</v>
+        <v>355.0187119470689</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>143</v>
+        <v>51.6</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.01399777908643</v>
+        <v>50.1666281495004</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>17.36199313882288</v>
+        <v>17.28403047352334</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6056307244439875</v>
+        <v>0.5898495629800935</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.5420628163513347</v>
+        <v>-0.0431077101336801</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6281</v>
+        <v>6187</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>355.0187119470689</v>
+        <v>354.5936112175816</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>51.6</v>
+        <v>1090</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,49 +2513,49 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>50.1666281495004</v>
+        <v>53.46111170044246</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>17.28403047352334</v>
+        <v>12.3087041217293</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5898495629800935</v>
+        <v>1.514857326548334</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.0431077101336801</v>
+        <v>22.09232555567394</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6187</v>
+        <v>6175</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>354.5936112175816</v>
+        <v>348.4476963018541</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1090</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,49 +2566,49 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>53.46111170044246</v>
+        <v>38.72763810708439</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>12.3087041217293</v>
+        <v>25.87997541245723</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.514857326548334</v>
+        <v>0.3590619387938579</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>22.09232555567394</v>
+        <v>-0.0359591325848578</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6175</v>
+        <v>6194</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>348.4476963018541</v>
+        <v>347.7573265565226</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>30</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>38.72763810708439</v>
+        <v>43.18199965040478</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>25.87997541245723</v>
+        <v>28.94073767614961</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3590619387938579</v>
+        <v>0.7278523181695278</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.0359591325848578</v>
+        <v>0.0906848257259589</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6194</v>
+        <v>6163</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>347.7573265565226</v>
+        <v>338.2535835834404</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>43.18199965040478</v>
+        <v>47.96628956233509</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>28.94073767614961</v>
+        <v>27.96189953778999</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.7278523181695278</v>
+        <v>0.42215608371619</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0906848257259589</v>
+        <v>0.5647133368152435</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6285</v>
+        <v>6449</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>344.6446341049075</v>
+        <v>327.6955893517073</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>256</v>
+        <v>240.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>53.1038400026636</v>
+        <v>44.6919693221508</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>19.05769318803712</v>
+        <v>31.57261110678408</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.288124327605217</v>
+        <v>0.7398891102966632</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>2.422875656530869</v>
+        <v>4.239608341688111</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6278</v>
+        <v>6224</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>338.6762966894772</v>
+        <v>324.8592085479777</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>171.5</v>
+        <v>56</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>52.11554347801326</v>
+        <v>42.21910147936961</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>28.39550416933267</v>
+        <v>32.83834489354695</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.535899867764819</v>
+        <v>0.4784450780377132</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>3.261276972419939</v>
+        <v>0.8945242461589924</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6163</v>
+        <v>6166</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>338.2535835834404</v>
+        <v>323.2439352713656</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>47.96628956233509</v>
+        <v>54.01399777908643</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>27.96189953778999</v>
+        <v>17.36199313882288</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.42215608371619</v>
+        <v>0.6056307244439875</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.5647133368152435</v>
+        <v>0.5420628163513347</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6197</v>
+        <v>6278</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>330.7420034366085</v>
+        <v>318.6762966894772</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>309</v>
+        <v>171.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>49.27257213589504</v>
+        <v>52.11554347801326</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>19.20985592526348</v>
+        <v>28.39550416933267</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.9648127531215788</v>
+        <v>1.535899867764819</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.9338417424029366</v>
+        <v>3.261276972419939</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6239</v>
+        <v>6477</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>319.235622848787</v>
+        <v>316.4502613287738</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>288.5</v>
+        <v>33.95</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>52.97887863304339</v>
+        <v>43.37166705898985</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>16.93969890618489</v>
+        <v>16.97922797804473</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.3712256943201117</v>
+        <v>0.2215247056356196</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>3.553993633587414</v>
+        <v>-0.5107340494142445</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6442</v>
+        <v>6220</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>295.8860407547625</v>
+        <v>309.8850668686963</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>1425</v>
+        <v>25.75</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.16117003979465</v>
+        <v>35.84961710887379</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.67396318234185</v>
+        <v>30.8699502661992</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.204091036502204</v>
+        <v>0.7666573207713016</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>39.23105388440921</v>
+        <v>0.0596857528714043</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6208</v>
+        <v>6285</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>291.3313815875944</v>
+        <v>304.6446341049075</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>81.7</v>
+        <v>256</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44.02708707802903</v>
+        <v>53.1038400026636</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>16.66578478987826</v>
+        <v>19.05769318803712</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.9407008158382956</v>
+        <v>1.288124327605217</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.2488588667002425</v>
+        <v>2.422875656530869</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6272</v>
+        <v>6223</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>287.9809485687836</v>
+        <v>291.7388476456422</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>25.1</v>
+        <v>6225</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>39.49926573118158</v>
+        <v>53.77850832992098</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>40.31524748927225</v>
+        <v>13.95167726939298</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3040456642072235</v>
+        <v>1.234844571663057</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.1578583735868139</v>
+        <v>94.52794024248088</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6477</v>
+        <v>6208</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>286.4502613287738</v>
+        <v>291.3313815875944</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>33.95</v>
+        <v>81.7</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>43.37166705898985</v>
+        <v>44.02708707802903</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.97922797804473</v>
+        <v>16.66578478987826</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.2215247056356196</v>
+        <v>0.9407008158382956</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.5107340494142445</v>
+        <v>0.2488588667002425</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6415</v>
+        <v>6197</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>283.6435242083139</v>
+        <v>290.7420034366085</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>465</v>
+        <v>309</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>49.33236413881773</v>
+        <v>49.27257213589504</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.58562664275986</v>
+        <v>19.20985592526348</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6589164054743736</v>
+        <v>0.9648127531215788</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>6.783230712566947</v>
+        <v>0.9338417424029366</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6209</v>
+        <v>6272</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>272.9438452146628</v>
+        <v>287.9809485687836</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>74</v>
+        <v>25.1</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.72679550536951</v>
+        <v>39.49926573118158</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>16.91662821541473</v>
+        <v>40.31524748927225</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.9282442957113188</v>
+        <v>0.3040456642072235</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>1.402312812022273</v>
+        <v>0.1578583735868139</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6230</v>
+        <v>6443</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>262.8933382391858</v>
+        <v>281.8605787463625</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>110</v>
+        <v>27.05</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>41.08825921834021</v>
+        <v>43.89761042925628</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>30.74406490376641</v>
+        <v>28.15759170920897</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5781209613052208</v>
+        <v>0.7605653134049977</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.4429766073275809</v>
+        <v>0.4570613136076846</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6443</v>
+        <v>6239</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>251.8605787463625</v>
+        <v>279.235622848787</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>27.05</v>
+        <v>288.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>43.89761042925628</v>
+        <v>52.97887863304339</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>28.15759170920897</v>
+        <v>16.93969890618489</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7605653134049977</v>
+        <v>0.3712256943201117</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.4570613136076846</v>
+        <v>3.553993633587414</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6176</v>
+        <v>6442</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>243.100983376216</v>
+        <v>275.8860407547625</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>82.3</v>
+        <v>1425</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>38.46487597265871</v>
+        <v>51.16117003979465</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.68537825760686</v>
+        <v>23.67396318234185</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7036948869608187</v>
+        <v>1.204091036502204</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0270765751039372</v>
+        <v>39.23105388440921</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6205</v>
+        <v>6176</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>239.1524623542154</v>
+        <v>273.1009833762159</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>61.5</v>
+        <v>82.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>46.45508190768687</v>
+        <v>38.46487597265871</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>29.75215094360628</v>
+        <v>21.68537825760686</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4889966154262554</v>
+        <v>0.7036948869608187</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>1.012582027457825</v>
+        <v>-0.0270765751039372</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6185</v>
+        <v>6230</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>222.885131429598</v>
+        <v>262.8933382391858</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>13.7</v>
+        <v>110</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>42.6877721119601</v>
+        <v>41.08825921834021</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11.59677679826853</v>
+        <v>30.74406490376641</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5026616149427816</v>
+        <v>0.5781209613052208</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0236661808038683</v>
+        <v>0.4429766073275809</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6170</v>
+        <v>6415</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>217.6497984685856</v>
+        <v>243.6435242083139</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>46.75</v>
+        <v>465</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>40.77890060401315</v>
+        <v>49.33236413881773</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>35.72179169242083</v>
+        <v>20.58562664275986</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.661861197280782</v>
+        <v>0.6589164054743736</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.187081502455551</v>
+        <v>6.783230712566947</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6283</v>
+        <v>6209</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>208.5046970566998</v>
+        <v>232.9438452146628</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>20.15</v>
+        <v>74</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>35.31092862846783</v>
+        <v>51.72679550536951</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>37.15218989297408</v>
+        <v>16.91662821541473</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.8323686662273455</v>
+        <v>0.9282442957113188</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0628677858006557</v>
+        <v>1.402312812022273</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6189</v>
+        <v>6185</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>201.1319985267957</v>
+        <v>222.885131429598</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>49.05</v>
+        <v>13.7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.67352634775676</v>
+        <v>42.6877721119601</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>12.19694852122346</v>
+        <v>11.59677679826853</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.145919097776142</v>
+        <v>0.5026616149427816</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.3153184743380142</v>
+        <v>-0.0236661808038683</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6218</v>
+        <v>6170</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>200.3602628461556</v>
+        <v>217.6497984685856</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>36.1</v>
+        <v>46.75</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>56.54724414854483</v>
+        <v>40.77890060401315</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>12.02101610242847</v>
+        <v>35.72179169242083</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7414174001576361</v>
+        <v>0.661861197280782</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.4270261059824491</v>
+        <v>0.187081502455551</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6167</v>
+        <v>6283</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>187.6680419392304</v>
+        <v>208.5046970566998</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>10.6</v>
+        <v>20.15</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>44.20309361337731</v>
+        <v>35.31092862846783</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>22.00275520034725</v>
+        <v>37.15218989297408</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3641089052041301</v>
+        <v>0.8323686662273455</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0452256904481102</v>
+        <v>0.0628677858006557</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6438</v>
+        <v>6218</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>179.9651212431265</v>
+        <v>200.3602628461556</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>147</v>
+        <v>36.1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>50.75119064629824</v>
+        <v>56.54724414854483</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>22.69980200634814</v>
+        <v>12.02101610242847</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3696585347344731</v>
+        <v>0.7414174001576361</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>1.34823973745081</v>
+        <v>0.4270261059824491</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6198</v>
+        <v>6205</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>174.9873341557976</v>
+        <v>199.1524623542154</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>19.5</v>
+        <v>61.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>51.65137386098494</v>
+        <v>46.45508190768687</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>8.727524867207372</v>
+        <v>29.75215094360628</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.2155079676989056</v>
+        <v>0.4889966154262554</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,11 +3909,11 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.4388121450622013</v>
+        <v>1.012582027457825</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>163.1788798683914</v>
+        <v>193.1788798683914</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>39.95</v>
@@ -3972,21 +3972,21 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6201</v>
+        <v>6228</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>137.3786017942331</v>
+        <v>193.0968173881948</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>45.45</v>
+        <v>17.55</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>29.22608246598594</v>
+        <v>51.12407703518314</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15.86518354650595</v>
+        <v>10.26916350645334</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6357624002122155</v>
+        <v>1.672024406724134</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.4331030236711123</v>
+        <v>0.4135605846389678</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6210</v>
+        <v>6167</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>136.6174210068478</v>
+        <v>187.6680419392304</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>17.05</v>
+        <v>10.6</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.11131091030587</v>
+        <v>44.20309361337731</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>14.89637987282742</v>
+        <v>22.00275520034725</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.9651835149133774</v>
+        <v>0.3641089052041301</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.2569601624107177</v>
+        <v>0.0452256904481102</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6235</v>
+        <v>6189</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>96.75640038535536</v>
+        <v>181.1319985267957</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>39.75</v>
+        <v>49.05</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.11386746324438</v>
+        <v>50.67352634775676</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>14.18654942921434</v>
+        <v>12.19694852122346</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.3431481457556441</v>
+        <v>1.145919097776142</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.2829840148598264</v>
+        <v>0.3153184743380142</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6216</v>
+        <v>6438</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>92.14896717171855</v>
+        <v>179.9651212431265</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>21.9</v>
+        <v>147</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>43.51445079833805</v>
+        <v>50.75119064629824</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>13.68004799884843</v>
+        <v>22.69980200634814</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.9975319181756408</v>
+        <v>0.3696585347344731</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,62 +4174,433 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0326616722666913</v>
+        <v>1.34823973745081</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
+        <v>6198</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>瑞築</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>174.9873341557976</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>51.65137386098494</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>8.727524867207372</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0.2155079676989056</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>0.4388121450622013</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>6233</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>旺玖</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>165.6092593287854</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>48.04640689254035</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>30.6112588544335</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.6623345041445429</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>0.1508209022986544</v>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>亞弘電</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>137.3786017942331</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>29.22608246598594</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>15.86518354650595</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0.6357624002122155</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>-0.4331030236711123</v>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>慶生</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>136.6174210068478</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>49.11131091030587</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>14.89637987282742</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>0.9651835149133774</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>0.2569601624107177</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>6216</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>居易</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>122.1489671717186</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>43.51445079833805</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>13.68004799884843</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>0.9975319181756408</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>0.0326616722666913</v>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>6222</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>立軒</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>118.2392456072611</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>51.16310915159138</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>16.04776659063952</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>2.52432492101957</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>-0.0834759897303574</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>6235</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>華孚</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>96.75640038535536</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>51.11386746324438</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>14.18654942921434</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>0.3431481457556441</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>0.2829840148598264</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
         <v>6203</v>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>海韻電</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D71" s="2" t="n">
+      <c r="C78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D78" s="2" t="n">
         <v>91.27343946356822</v>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E78" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H71" s="2" t="n">
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
         <v>31.63659554236342</v>
       </c>
-      <c r="I71" s="2" t="n">
+      <c r="I78" s="2" t="n">
         <v>16.32956395134587</v>
       </c>
-      <c r="J71" s="2" t="n">
+      <c r="J78" s="2" t="n">
         <v>0.8303317927924019</v>
       </c>
-      <c r="K71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N71" s="2" t="n">
+      <c r="K78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N78" s="2" t="n">
         <v>-0.4010030504976853</v>
       </c>
-      <c r="O71" s="2" t="inlineStr">
+      <c r="O78" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq6_2026-08-10.xlsx
+++ b/output/full_scan/batch_seq6_2026-08-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6183</v>
+        <v>6245</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>759.0715295797295</v>
+        <v>1179.609260862679</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>57.72972358501564</v>
+        <v>64.14845239485086</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>24.80649994338685</v>
+        <v>13.1959849840415</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.8393055552133863</v>
+        <v>2.736214217402912</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0516142484460759</v>
+        <v>0.9594501942029938</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6206</v>
+        <v>6474</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>741.4295398605429</v>
+        <v>1071.035274387684</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>158</v>
+        <v>39.1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>69.8519648258317</v>
+        <v>58.72097373925624</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>22.36509063639624</v>
+        <v>7.576334130101467</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.2429539860543</v>
+        <v>4.703527438768361</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>3.356136910500504</v>
+        <v>0.1376064599923991</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6277</v>
+        <v>6279</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>699.9007446685157</v>
+        <v>1036.279370656238</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>58.28217218426251</v>
+        <v>71.17060287906786</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>40.03009108109279</v>
+        <v>17.76872230241968</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.3738124525140116</v>
+        <v>4.727937065623767</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.0431276750575646</v>
+        <v>1.539746394479904</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6409</v>
+        <v>6265</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>674.298599291236</v>
+        <v>1013.320548072234</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1040</v>
+        <v>55.8</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>56.65274257204385</v>
+        <v>61.32624523855267</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>18.3546278662841</v>
+        <v>20.18808496908987</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.087510803751077</v>
+        <v>2.044070488003614</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>3.359800838702622</v>
+        <v>1.485442790338732</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6423</v>
+        <v>6418</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>646.479123855205</v>
+        <v>933.9851028162832</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>33.85</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>62.04457810321975</v>
+        <v>60.90780365109744</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>24.75648321415393</v>
+        <v>16.3692608756217</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.364080393908019</v>
+        <v>2.119191967652007</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>2</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.871420111893109</v>
+        <v>0.3704794100607577</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6426</v>
+        <v>6446</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>627.2407417551258</v>
+        <v>882.151994707984</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>217.5</v>
+        <v>1330</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>65.00891190168468</v>
+        <v>59.04327038318963</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23.59125144904065</v>
+        <v>23.91395117110724</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.528340892861066</v>
+        <v>1.32647631086369</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>8.13280202667679</v>
+        <v>12.92287894752021</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6174</v>
+        <v>6472</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>588.7947111834289</v>
+        <v>764.6801525580941</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>42.1</v>
+        <v>431</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>42.64256723209201</v>
+        <v>59.10000972767694</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>27.08809261864932</v>
+        <v>20.39286277565401</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6669427503235502</v>
+        <v>1.095268557074715</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.2637432742458458</v>
+        <v>3.920457640854598</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6213</v>
+        <v>6183</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>567.5732718092964</v>
+        <v>759.0715295797295</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>427.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>68.17267535409505</v>
+        <v>57.72972358501564</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>21.01192449358658</v>
+        <v>24.80649994338685</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.939831190477381</v>
+        <v>0.8393055552133863</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>12.04988962019979</v>
+        <v>0.0516142484460759</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6416</v>
+        <v>6435</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>559.7392298105297</v>
+        <v>757.240522201329</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>103.5</v>
+        <v>258.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.07306364228874</v>
+        <v>44.84781913821785</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>22.36052036738694</v>
+        <v>30.28700159150673</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.8541636234026162</v>
+        <v>0.5121481807668025</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4293684829413609</v>
+        <v>0.5056738271099945</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6225</v>
+        <v>6206</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>557.5305158178907</v>
+        <v>741.4295398605429</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>27.7</v>
+        <v>158</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>63.86523044436224</v>
+        <v>69.8519648258317</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>14.97469433694032</v>
+        <v>22.36509063639624</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.371576731818218</v>
+        <v>2.2429539860543</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.2549384159791399</v>
+        <v>3.356136910500504</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6243</v>
+        <v>6277</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>546.8279966440317</v>
+        <v>699.9007446685157</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>45.7</v>
+        <v>80</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>49.73499215487036</v>
+        <v>58.28217218426251</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>24.50252557516282</v>
+        <v>40.03009108109279</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4275410613229602</v>
+        <v>0.3738124525140116</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.775992343674111</v>
+        <v>0.0431276750575646</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6165</v>
+        <v>6409</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>546.0837748536428</v>
+        <v>674.298599291236</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>50.9</v>
+        <v>1040</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>57.42647306499502</v>
+        <v>56.65274257204385</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15.63548067020227</v>
+        <v>18.3546278662841</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4083774853642788</v>
+        <v>1.087510803751077</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1674920369763979</v>
+        <v>3.359800838702622</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6173</v>
+        <v>6441</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>541.4106605656436</v>
+        <v>674</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>168.5</v>
+        <v>23.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>42.68472073119765</v>
+        <v>64.10774332944138</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>34.40595260796817</v>
+        <v>17.22544281154968</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.192593663939603</v>
+        <v>7.613158742628346</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>2.050485919277733</v>
+        <v>0.4472917125471358</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6414</v>
+        <v>6423</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>538.6962739065256</v>
+        <v>646.479123855205</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>482</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>63.98893928656253</v>
+        <v>62.04457810321975</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>22.63266797071104</v>
+        <v>24.75648321415393</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5780998580566509</v>
+        <v>2.364080393908019</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.853520720826112</v>
+        <v>1.871420111893109</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6257</v>
+        <v>6291</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>534.4171668524763</v>
+        <v>638.5022240217937</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>207.5</v>
+        <v>383.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>48.23670684236492</v>
+        <v>46.24097433206729</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>20.23025813225657</v>
+        <v>28.75805544915245</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.105316696941825</v>
+        <v>0.6893718995474601</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.5372968428071516</v>
+        <v>10.20613627363809</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6196</v>
+        <v>6426</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>510.7388291927062</v>
+        <v>627.2407417551258</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>507</v>
+        <v>217.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>48.94670338794104</v>
+        <v>65.00891190168468</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>18.17108286298426</v>
+        <v>23.59125144904065</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5649022304227247</v>
+        <v>3.528340892861066</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.09659835150966239</v>
+        <v>8.13280202667679</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6207</v>
+        <v>6177</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>493.1233910795527</v>
+        <v>605.3195370923144</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>107</v>
+        <v>48.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>45.35352010472476</v>
+        <v>60.66793577424178</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>24.01990798366345</v>
+        <v>25.97872362834705</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8414466540819895</v>
+        <v>1.154768422456902</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0129623380944003</v>
+        <v>0.0405206509433421</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6191</v>
+        <v>6419</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>486.5213487682032</v>
+        <v>600.6027058268821</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>87.2</v>
+        <v>145</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>46.10082338888115</v>
+        <v>55.16416624107681</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>32.47729147557256</v>
+        <v>12.82628546363621</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.9069630681754032</v>
+        <v>1.133036544191641</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3827828243389604</v>
+        <v>2.118238812262394</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6188</v>
+        <v>6174</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>474.8406128108113</v>
+        <v>588.7947111834289</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>42.1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>49.80207136706857</v>
+        <v>42.64256723209201</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>25.52727840673741</v>
+        <v>27.08809261864932</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5760718298255886</v>
+        <v>0.6669427503235502</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>1</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.7769172661227373</v>
+        <v>-0.2637432742458458</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6192</v>
+        <v>6263</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>472.8844005003289</v>
+        <v>584.2319319427455</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>50.71970970820144</v>
+        <v>55.87991564524722</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27.63184573698078</v>
+        <v>12.47242753246073</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.803305208082017</v>
+        <v>1.259876850523356</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.6284810867254307</v>
+        <v>1.556040969952073</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6226</v>
+        <v>6213</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>471.1181302095761</v>
+        <v>567.5732718092964</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>21.4</v>
+        <v>427.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>51.85707165608408</v>
+        <v>68.17267535409505</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>21.64916109257221</v>
+        <v>21.01192449358658</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.7261193329042747</v>
+        <v>0.939831190477381</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.0858684090367485</v>
+        <v>12.04988962019979</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6202</v>
+        <v>6290</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>468.6656967592002</v>
+        <v>560.0836455210743</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>63.8</v>
+        <v>214</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.74697808965778</v>
+        <v>38.61672807273666</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>20.446544188162</v>
+        <v>36.90595802568092</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7603994648675344</v>
+        <v>1.129133296042357</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.117314594431419</v>
+        <v>0.7932520256254811</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6269</v>
+        <v>6416</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>467.3790662214192</v>
+        <v>559.7392298105297</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>103.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>59.06299385342777</v>
+        <v>61.07306364228874</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>23.02567040809344</v>
+        <v>22.36052036738694</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.755810145246609</v>
+        <v>0.8541636234026162</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2.098634061476899</v>
+        <v>0.4293684829413609</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6214</v>
+        <v>6225</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>465.1093242918259</v>
+        <v>557.5305158178907</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>144.5</v>
+        <v>27.7</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>51.90361828462773</v>
+        <v>63.86523044436224</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>13.55674118232764</v>
+        <v>14.97469433694032</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.7395676640936464</v>
+        <v>1.371576731818218</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.0686585128964987</v>
+        <v>0.2549384159791399</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6204</v>
+        <v>6243</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>434.4520395977325</v>
+        <v>546.8279966440317</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>45.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>49.38479745912756</v>
+        <v>49.73499215487036</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>32.70946694624664</v>
+        <v>24.50252557516282</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2.159783213308927</v>
+        <v>0.4275410613229602</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>2.195641091635059</v>
+        <v>-0.775992343674111</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6456</v>
+        <v>6165</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>429.5605218768488</v>
+        <v>546.0837748536428</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>50.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.7413526864353</v>
+        <v>57.42647306499502</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>19.71368861988782</v>
+        <v>15.63548067020227</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.826702105975958</v>
+        <v>0.4083774853642788</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.9622575759652472</v>
+        <v>0.1674920369763979</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6412</v>
+        <v>6292</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>426.4269401657284</v>
+        <v>545.7971518881778</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>79.40000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>43.0442641973437</v>
+        <v>59.40030270591252</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>32.45947676384331</v>
+        <v>19.22248740125504</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.6196459418887108</v>
+        <v>1.266396976409842</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.3570158784420925</v>
+        <v>1.337499257142632</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6215</v>
+        <v>6462</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>404.0955443326735</v>
+        <v>542.9742200222066</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>102.5</v>
+        <v>101.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.4831845416134</v>
+        <v>48.88161223958439</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>20.62292992617979</v>
+        <v>22.70688394128613</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.618470111238015</v>
+        <v>0.7342339574899936</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.603861921628523</v>
+        <v>1.322704217753153</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6227</v>
+        <v>6173</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>400.5733654378773</v>
+        <v>541.4106605656436</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>125</v>
+        <v>168.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>59.6060879416657</v>
+        <v>42.68472073119765</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>14.62738190139732</v>
+        <v>34.40595260796817</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.7786837377881891</v>
+        <v>1.192593663939603</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>1.726766377538268</v>
+        <v>2.050485919277733</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6451</v>
+        <v>6414</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>392.1336928623746</v>
+        <v>538.6962739065256</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>51.91723260762927</v>
+        <v>63.98893928656253</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.75121944207835</v>
+        <v>22.63266797071104</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.17541246209539</v>
+        <v>0.5780998580566509</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>11.18580724096196</v>
+        <v>1.853520720826112</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6229</v>
+        <v>6257</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>390.7053521503887</v>
+        <v>534.4171668524763</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>23.55</v>
+        <v>207.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>44.50445772105656</v>
+        <v>48.23670684236492</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23.71939551545771</v>
+        <v>20.23025813225657</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.2669724967060971</v>
+        <v>1.105316696941825</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1581766699771224</v>
+        <v>0.5372968428071516</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6282</v>
+        <v>6196</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>390.5686398964842</v>
+        <v>510.7388291927062</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>50</v>
+        <v>507</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>51.06184388891582</v>
+        <v>48.94670338794104</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22.93307245830036</v>
+        <v>18.17108286298426</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.04928995115029</v>
+        <v>0.5649022304227247</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.7979662344550689</v>
+        <v>0.09659835150966239</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6164</v>
+        <v>6284</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>389.9545860402761</v>
+        <v>506.6437991104705</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>42.92545485830978</v>
+        <v>42.98606729105794</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>28.85861796316664</v>
+        <v>28.35930946124841</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.2785208213487328</v>
+        <v>0.6080822135887535</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0073923597656112</v>
+        <v>0.6272163222006935</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6271</v>
+        <v>6207</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>385.8236690474123</v>
+        <v>493.1233910795527</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>197</v>
+        <v>107</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>48.91352016282462</v>
+        <v>45.35352010472476</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>23.13023124621723</v>
+        <v>24.01990798366345</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.9825193022842416</v>
+        <v>0.8414466540819895</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>3.554357245802505</v>
+        <v>0.0129623380944003</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6168</v>
+        <v>6191</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>385.5998715595856</v>
+        <v>486.5213487682032</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>25.05</v>
+        <v>87.2</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>50.14145864011715</v>
+        <v>46.10082338888115</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>21.92519634713251</v>
+        <v>32.47729147557256</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.920718696931504</v>
+        <v>0.9069630681754032</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3851070248310393</v>
+        <v>0.3827828243389604</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6190</v>
+        <v>6188</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>371.4921416834692</v>
+        <v>474.8406128108113</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>68.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>47.05627038961318</v>
+        <v>49.80207136706857</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>32.08947107167344</v>
+        <v>25.52727840673741</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.8270287635314424</v>
+        <v>0.5760718298255886</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>1</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.5251318219281336</v>
+        <v>0.7769172661227373</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6281</v>
+        <v>6192</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>355.0187119470689</v>
+        <v>472.8844005003289</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>51.6</v>
+        <v>116</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>50.1666281495004</v>
+        <v>50.71970970820144</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>17.28403047352334</v>
+        <v>27.63184573698078</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.5898495629800935</v>
+        <v>1.803305208082017</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.0431077101336801</v>
+        <v>0.6284810867254307</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6187</v>
+        <v>6226</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>354.5936112175816</v>
+        <v>471.1181302095761</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1090</v>
+        <v>21.4</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,49 +2513,49 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>53.46111170044246</v>
+        <v>51.85707165608408</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>12.3087041217293</v>
+        <v>21.64916109257221</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.514857326548334</v>
+        <v>0.7261193329042747</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>22.09232555567394</v>
+        <v>-0.0858684090367485</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6175</v>
+        <v>6202</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>348.4476963018541</v>
+        <v>468.6656967592002</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>38.72763810708439</v>
+        <v>56.74697808965778</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>25.87997541245723</v>
+        <v>20.446544188162</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3590619387938579</v>
+        <v>0.7603994648675344</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.0359591325848578</v>
+        <v>1.117314594431419</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6194</v>
+        <v>6269</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>347.7573265565226</v>
+        <v>467.3790662214192</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>30</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>43.18199965040478</v>
+        <v>59.06299385342777</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>28.94073767614961</v>
+        <v>23.02567040809344</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.7278523181695278</v>
+        <v>1.755810145246609</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0906848257259589</v>
+        <v>2.098634061476899</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6163</v>
+        <v>6214</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>338.2535835834404</v>
+        <v>465.1093242918259</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>42</v>
+        <v>144.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>47.96628956233509</v>
+        <v>51.90361828462773</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>27.96189953778999</v>
+        <v>13.55674118232764</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.42215608371619</v>
+        <v>0.7395676640936464</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.5647133368152435</v>
+        <v>-0.0686585128964987</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6449</v>
+        <v>6204</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>327.6955893517073</v>
+        <v>434.4520395977325</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>240.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>44.6919693221508</v>
+        <v>49.38479745912756</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>31.57261110678408</v>
+        <v>32.70946694624664</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7398891102966632</v>
+        <v>2.159783213308927</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>4.239608341688111</v>
+        <v>2.195641091635059</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6224</v>
+        <v>6456</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>324.8592085479777</v>
+        <v>429.5605218768488</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>56</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>42.21910147936961</v>
+        <v>55.7413526864353</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>32.83834489354695</v>
+        <v>19.71368861988782</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4784450780377132</v>
+        <v>1.826702105975958</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.8945242461589924</v>
+        <v>0.9622575759652472</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6166</v>
+        <v>6412</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>323.2439352713656</v>
+        <v>426.4269401657284</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>143</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>54.01399777908643</v>
+        <v>43.0442641973437</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>17.36199313882288</v>
+        <v>32.45947676384331</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6056307244439875</v>
+        <v>0.6196459418887108</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.5420628163513347</v>
+        <v>0.3570158784420925</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6278</v>
+        <v>6266</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>318.6762966894772</v>
+        <v>418.2379101641095</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>171.5</v>
+        <v>24.95</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>52.11554347801326</v>
+        <v>51.21122352889414</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>28.39550416933267</v>
+        <v>21.49130053752384</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.535899867764819</v>
+        <v>0.6701876753271021</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>3.261276972419939</v>
+        <v>0.0713782870170524</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6477</v>
+        <v>6237</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>316.4502613287738</v>
+        <v>417.7723568880295</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>33.95</v>
+        <v>34.4</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>43.37166705898985</v>
+        <v>41.61819725769668</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>16.97922797804473</v>
+        <v>34.45406225923031</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2215247056356196</v>
+        <v>0.969753099301384</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.5107340494142445</v>
+        <v>0.4350925517495589</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6220</v>
+        <v>6261</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>309.8850668686963</v>
+        <v>414.4738028777282</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>25.75</v>
+        <v>78.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>35.84961710887379</v>
+        <v>40.78955072974081</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>30.8699502661992</v>
+        <v>34.0133539614609</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7666573207713016</v>
+        <v>0.4997657215506068</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>1</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0596857528714043</v>
+        <v>0.6561123674882667</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6285</v>
+        <v>6215</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>304.6446341049075</v>
+        <v>404.0955443326735</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>256</v>
+        <v>102.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>53.1038400026636</v>
+        <v>54.4831845416134</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>19.05769318803712</v>
+        <v>20.62292992617979</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.288124327605217</v>
+        <v>1.618470111238015</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>2.422875656530869</v>
+        <v>1.603861921628523</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6223</v>
+        <v>6227</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>291.7388476456422</v>
+        <v>400.5733654378773</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>6225</v>
+        <v>125</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>53.77850832992098</v>
+        <v>59.6060879416657</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>13.95167726939298</v>
+        <v>14.62738190139732</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.234844571663057</v>
+        <v>0.7786837377881891</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>94.52794024248088</v>
+        <v>1.726766377538268</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6208</v>
+        <v>6451</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>291.3313815875944</v>
+        <v>392.1336928623746</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>81.7</v>
+        <v>456</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>44.02708707802903</v>
+        <v>51.91723260762927</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.66578478987826</v>
+        <v>20.75121944207835</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9407008158382956</v>
+        <v>1.17541246209539</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.2488588667002425</v>
+        <v>11.18580724096196</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6197</v>
+        <v>6229</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>290.7420034366085</v>
+        <v>390.7053521503887</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>309</v>
+        <v>23.55</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>49.27257213589504</v>
+        <v>44.50445772105656</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>19.20985592526348</v>
+        <v>23.71939551545771</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9648127531215788</v>
+        <v>0.2669724967060971</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.9338417424029366</v>
+        <v>0.1581766699771224</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6272</v>
+        <v>6282</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>287.9809485687836</v>
+        <v>390.5686398964842</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>25.1</v>
+        <v>50</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>39.49926573118158</v>
+        <v>51.06184388891582</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>40.31524748927225</v>
+        <v>22.93307245830036</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3040456642072235</v>
+        <v>1.04928995115029</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1578583735868139</v>
+        <v>0.7979662344550689</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6443</v>
+        <v>6164</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>281.8605787463625</v>
+        <v>389.9545860402761</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>27.05</v>
+        <v>11.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>43.89761042925628</v>
+        <v>42.92545485830978</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>28.15759170920897</v>
+        <v>28.85861796316664</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7605653134049977</v>
+        <v>0.2785208213487328</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.4570613136076846</v>
+        <v>0.0073923597656112</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6239</v>
+        <v>6244</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>279.235622848787</v>
+        <v>387.633140346601</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>288.5</v>
+        <v>24.1</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>52.97887863304339</v>
+        <v>47.17959685929374</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>16.93969890618489</v>
+        <v>20.20737747570019</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.3712256943201117</v>
+        <v>0.5960173661677242</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>3.553993633587414</v>
+        <v>0.1845319791670452</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6442</v>
+        <v>6241</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>275.8860407547625</v>
+        <v>387.495923516295</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1425</v>
+        <v>14.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>51.16117003979465</v>
+        <v>42.29653498322487</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>23.67396318234185</v>
+        <v>24.04408865973238</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.204091036502204</v>
+        <v>1.133226105360458</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>39.23105388440921</v>
+        <v>-0.2890136925922362</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6176</v>
+        <v>6271</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>273.1009833762159</v>
+        <v>385.8236690474123</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>82.3</v>
+        <v>197</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>38.46487597265871</v>
+        <v>48.91352016282462</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>21.68537825760686</v>
+        <v>23.13023124621723</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.7036948869608187</v>
+        <v>0.9825193022842416</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0270765751039372</v>
+        <v>3.554357245802505</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6230</v>
+        <v>6168</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>262.8933382391858</v>
+        <v>385.5998715595856</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>110</v>
+        <v>25.05</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>41.08825921834021</v>
+        <v>50.14145864011715</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>30.74406490376641</v>
+        <v>21.92519634713251</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5781209613052208</v>
+        <v>0.920718696931504</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.4429766073275809</v>
+        <v>0.3851070248310393</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6415</v>
+        <v>6190</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>243.6435242083139</v>
+        <v>371.4921416834692</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>465</v>
+        <v>68.8</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>49.33236413881773</v>
+        <v>47.05627038961318</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.58562664275986</v>
+        <v>32.08947107167344</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6589164054743736</v>
+        <v>0.8270287635314424</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>6.783230712566947</v>
+        <v>0.5251318219281336</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6209</v>
+        <v>6275</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>232.9438452146628</v>
+        <v>365.6140232494847</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>74</v>
+        <v>44.35</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>51.72679550536951</v>
+        <v>48.01353109129185</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>16.91662821541473</v>
+        <v>27.30768493519729</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.9282442957113188</v>
+        <v>0.4451128516008499</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.402312812022273</v>
+        <v>0.3905624950238868</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6185</v>
+        <v>6234</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>222.885131429598</v>
+        <v>364.2015791794245</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>13.7</v>
+        <v>37.45</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>42.6877721119601</v>
+        <v>49.95387111707586</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>11.59677679826853</v>
+        <v>31.14785068882517</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5026616149427816</v>
+        <v>1.067020789595955</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0236661808038683</v>
+        <v>0.588770932873464</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6170</v>
+        <v>6417</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>217.6497984685856</v>
+        <v>363.458943530233</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>46.75</v>
+        <v>114</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>40.77890060401315</v>
+        <v>43.07614742376889</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>35.72179169242083</v>
+        <v>22.05913309705869</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.661861197280782</v>
+        <v>0.6024828405340277</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,51 +3750,51 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.187081502455551</v>
+        <v>0.6734983602673834</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6283</v>
+        <v>6288</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>208.5046970566998</v>
+        <v>361.3923632847385</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>20.15</v>
+        <v>20.95</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="G63" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>35.31092862846783</v>
+        <v>50.73723195180495</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>37.15218989297408</v>
+        <v>24.62449856753313</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8323686662273455</v>
+        <v>0.6831032524092705</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0628677858006557</v>
+        <v>0.0352967838852297</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6218</v>
+        <v>6281</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>200.3602628461556</v>
+        <v>355.0187119470689</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>36.1</v>
+        <v>51.6</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>56.54724414854483</v>
+        <v>50.1666281495004</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.02101610242847</v>
+        <v>17.28403047352334</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.7414174001576361</v>
+        <v>0.5898495629800935</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.4270261059824491</v>
+        <v>-0.0431077101336801</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6205</v>
+        <v>6187</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>199.1524623542154</v>
+        <v>354.5936112175816</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>61.5</v>
+        <v>1090</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,49 +3891,49 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>46.45508190768687</v>
+        <v>53.46111170044246</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>29.75215094360628</v>
+        <v>12.3087041217293</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4889966154262554</v>
+        <v>1.514857326548334</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>1.012582027457825</v>
+        <v>22.09232555567394</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6405</v>
+        <v>6175</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>193.1788798683914</v>
+        <v>348.4476963018541</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>39.95</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>40.25281645673567</v>
+        <v>38.72763810708439</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>30.86419512207522</v>
+        <v>25.87997541245723</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.8195290326940778</v>
+        <v>0.3590619387938579</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>1.003702836412715</v>
+        <v>-0.0359591325848578</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6228</v>
+        <v>6259</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>193.0968173881948</v>
+        <v>348.2139718282275</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>17.55</v>
+        <v>30.25</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.12407703518314</v>
+        <v>45.28407490891558</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>10.26916350645334</v>
+        <v>15.26406369707951</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.672024406724134</v>
+        <v>0.6323420804909667</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.4135605846389678</v>
+        <v>-0.2443625146511983</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6167</v>
+        <v>6194</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>187.6680419392304</v>
+        <v>347.7573265565226</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>10.6</v>
+        <v>30</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>44.20309361337731</v>
+        <v>43.18199965040478</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.00275520034725</v>
+        <v>28.94073767614961</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3641089052041301</v>
+        <v>0.7278523181695278</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0452256904481102</v>
+        <v>0.0906848257259589</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6189</v>
+        <v>6163</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>181.1319985267957</v>
+        <v>338.2535835834404</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>49.05</v>
+        <v>42</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.67352634775676</v>
+        <v>47.96628956233509</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>12.19694852122346</v>
+        <v>27.96189953778999</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.145919097776142</v>
+        <v>0.42215608371619</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3153184743380142</v>
+        <v>0.5647133368152435</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6438</v>
+        <v>6432</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>179.9651212431265</v>
+        <v>335.2555574679906</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>50.75119064629824</v>
+        <v>48.51706400938606</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>22.69980200634814</v>
+        <v>11.15009961210859</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3696585347344731</v>
+        <v>0.3262897680160447</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>1.34823973745081</v>
+        <v>-0.2548457274791474</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6198</v>
+        <v>6449</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>174.9873341557976</v>
+        <v>327.6955893517073</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>19.5</v>
+        <v>240.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.65137386098494</v>
+        <v>44.6919693221508</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8.727524867207372</v>
+        <v>31.57261110678408</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2155079676989056</v>
+        <v>0.7398891102966632</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.4388121450622013</v>
+        <v>4.239608341688111</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6233</v>
+        <v>6224</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>165.6092593287854</v>
+        <v>324.8592085479777</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>21.75</v>
+        <v>56</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.04640689254035</v>
+        <v>42.21910147936961</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>30.6112588544335</v>
+        <v>32.83834489354695</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6623345041445429</v>
+        <v>0.4784450780377132</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1508209022986544</v>
+        <v>0.8945242461589924</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6201</v>
+        <v>6166</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>137.3786017942331</v>
+        <v>323.2439352713656</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>45.45</v>
+        <v>143</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>29.22608246598594</v>
+        <v>54.01399777908643</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.86518354650595</v>
+        <v>17.36199313882288</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6357624002122155</v>
+        <v>0.6056307244439875</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.4331030236711123</v>
+        <v>0.5420628163513347</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6210</v>
+        <v>6278</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>136.6174210068478</v>
+        <v>318.6762966894772</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>17.05</v>
+        <v>171.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>49.11131091030587</v>
+        <v>52.11554347801326</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14.89637987282742</v>
+        <v>28.39550416933267</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.9651835149133774</v>
+        <v>1.535899867764819</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.2569601624107177</v>
+        <v>3.261276972419939</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6216</v>
+        <v>6477</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>122.1489671717186</v>
+        <v>316.4502613287738</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>21.9</v>
+        <v>33.95</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.51445079833805</v>
+        <v>43.37166705898985</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.68004799884843</v>
+        <v>16.97922797804473</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.9975319181756408</v>
+        <v>0.2215247056356196</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0326616722666913</v>
+        <v>-0.5107340494142445</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6222</v>
+        <v>6220</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>118.2392456072611</v>
+        <v>309.8850668686963</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>20.3</v>
+        <v>25.75</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>51.16310915159138</v>
+        <v>35.84961710887379</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.04776659063952</v>
+        <v>30.8699502661992</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2.52432492101957</v>
+        <v>0.7666573207713016</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0834759897303574</v>
+        <v>0.0596857528714043</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6235</v>
+        <v>6285</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>96.75640038535536</v>
+        <v>304.6446341049075</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>39.75</v>
+        <v>256</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>51.11386746324438</v>
+        <v>53.1038400026636</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>14.18654942921434</v>
+        <v>19.05769318803712</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3431481457556441</v>
+        <v>1.288124327605217</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,64 +4545,2025 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.2829840148598264</v>
+        <v>2.422875656530869</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
+        <v>6223</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>291.7388476456422</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>6225</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>53.77850832992098</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>13.95167726939298</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>1.234844571663057</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>94.52794024248088</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>日揚</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>291.3313815875944</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>44.02708707802903</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>16.66578478987826</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.9407008158382956</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>0.2488588667002425</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>6197</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>290.7420034366085</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>49.27257213589504</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>19.20985592526348</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.9648127531215788</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>0.9338417424029366</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>6270</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>倍微</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>289.8684890368287</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>47.46538629779184</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>18.33124375211008</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.5867715949856293</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>0.1936771203753526</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>6272</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>驊陞</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>287.9809485687836</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>39.49926573118158</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>40.31524748927225</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.3040456642072235</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0.1578583735868139</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>6443</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>元晶</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>281.8605787463625</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>43.89761042925628</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>28.15759170920897</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.7605653134049977</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>0.4570613136076846</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>晶焱</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>281.1484748602812</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>40.48921544309002</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>27.34333739810877</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.7468631112929144</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>0.5489169189527052</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>6239</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>279.235622848787</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>52.97887863304339</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>16.93969890618489</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>0.3712256943201117</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>3.553993633587414</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>6442</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>光聖</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>275.8860407547625</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>51.16117003979465</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>23.67396318234185</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>1.204091036502204</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>39.23105388440921</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>6176</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>瑞儀</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>273.1009833762159</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>38.46487597265871</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>21.68537825760686</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.7036948869608187</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>-0.0270765751039372</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>6464</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>台數科</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>267.8823795574915</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>40.82656933082557</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>25.02677514320827</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0.065236294480863</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>-0.245882857379472</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>6246</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>臺龍</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>264.8249002772042</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>34.26528640603611</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>28.34374301596924</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>1.018177299459957</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>0.0227246049556588</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>6230</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>尼得科超眾</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>262.8933382391858</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>41.08825921834021</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>30.74406490376641</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.5781209613052208</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>0.4429766073275809</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>6415</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>243.6435242083139</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>465</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>49.33236413881773</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>20.58562664275986</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.6589164054743736</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>6.783230712566947</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>今國光</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>232.9438452146628</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>51.72679550536951</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>16.91662821541473</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.9282442957113188</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>1.402312812022273</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>6185</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>幃翔</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>222.885131429598</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>42.6877721119601</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>11.59677679826853</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.5026616149427816</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>-0.0236661808038683</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>6184</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>大豐電</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>221.0170268886888</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>34.40920496107411</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>17.97741837521291</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.5463116788467773</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>0.0646109232731206</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>6170</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>統振</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>217.6497984685856</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>40.77890060401315</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>35.72179169242083</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.661861197280782</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>0.187081502455551</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>6283</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>淳安</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>208.5046970566998</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>35.31092862846783</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>37.15218989297408</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.8323686662273455</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>0.0628677858006557</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>6276</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>安鈦克</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>205.1862235174796</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>41.16487958159824</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>27.85311859203969</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>1.354076559036722</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>0.2144565645402201</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>6218</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>豪勉</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>200.3602628461556</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>56.54724414854483</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>12.02101610242847</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0.7414174001576361</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>0.4270261059824491</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>6205</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>詮欣</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>199.1524623542154</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>46.45508190768687</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>29.75215094360628</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.4889966154262554</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>1.012582027457825</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>6465</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>威潤</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>195.4064232862269</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>35.30386901845506</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>19.55251406453682</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.7325794743680427</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>-0.0776077778493684</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>6405</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>悅城</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>193.1788798683914</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>40.25281645673567</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>30.86419512207522</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.8195290326940778</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>1.003702836412715</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>6228</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>全譜</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>193.0968173881948</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>51.12407703518314</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>10.26916350645334</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>1.672024406724134</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>0.4135605846389678</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>6470</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>宇智</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>190.0500419868927</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>26.12614851885621</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>40.26161460050277</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.5633463129665093</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-0.2323863176250376</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>6167</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>久正</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>187.6680419392304</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>44.20309361337731</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>22.00275520034725</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.3641089052041301</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>0.0452256904481102</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>6189</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>豐藝</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>181.1319985267957</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>50.67352634775676</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>12.19694852122346</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>1.145919097776142</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>0.3153184743380142</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>6438</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>迅得</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>179.9651212431265</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>50.75119064629824</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>22.69980200634814</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.3696585347344731</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>1.34823973745081</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>6198</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>瑞築</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>174.9873341557976</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>51.65137386098494</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>8.727524867207372</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.2155079676989056</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>0.4388121450622013</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>6233</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>旺玖</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>165.6092593287854</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>48.04640689254035</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>30.6112588544335</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.6623345041445429</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>0.1508209022986544</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>亞弘電</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>137.3786017942331</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>29.22608246598594</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>15.86518354650595</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.6357624002122155</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>-0.4331030236711123</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>慶生</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>136.6174210068478</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>49.11131091030587</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>14.89637987282742</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.9651835149133774</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>0.2569601624107177</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>6216</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>居易</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>122.1489671717186</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>43.51445079833805</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>13.68004799884843</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.9975319181756408</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>0.0326616722666913</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>6222</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>立軒</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>118.2392456072611</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>51.16310915159138</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>16.04776659063952</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>2.52432492101957</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>-0.0834759897303574</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>6235</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>華孚</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>96.75640038535536</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>51.11386746324438</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>14.18654942921434</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.3431481457556441</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>0.2829840148598264</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
         <v>6203</v>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>海韻電</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D78" s="2" t="n">
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
         <v>91.27343946356822</v>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="E114" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H78" s="2" t="n">
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
         <v>31.63659554236342</v>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="I114" s="2" t="n">
         <v>16.32956395134587</v>
       </c>
-      <c r="J78" s="2" t="n">
+      <c r="J114" s="2" t="n">
         <v>0.8303317927924019</v>
       </c>
-      <c r="K78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N78" s="2" t="n">
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
         <v>-0.4010030504976853</v>
       </c>
-      <c r="O78" s="2" t="inlineStr">
+      <c r="O114" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>6236</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>中湛</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>48.11588819816776</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>4.29620370181045</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0.0626614403124483</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60</t>
         </is>
       </c>
     </row>
